--- a/Wikidata Delta/uz_gen_excels/pep_uzbekistan_living_relevant_cleaned.xlsx
+++ b/Wikidata Delta/uz_gen_excels/pep_uzbekistan_living_relevant_cleaned.xlsx
@@ -754,12 +754,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['Касимов Ойбек Омилович', 'Касимов Ойбек Омілович', 'Oybek Kasimov', 'Oybek Omilovich Kasimov', 'Oybek Kasimov Omilovich']</t>
+          <t>['Oybek Omilovich Kasimov', 'Oybek Kasimov Omilovich', 'Oybek Kasimov']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -845,11 +845,7 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Juge Ouzbekèke</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Fergana Region</t>
@@ -928,12 +924,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['Махмудова Робахон Анваровна', 'Robaxon Anvarovna Maxmudova', 'Robaxon Maxmudova', 'Robaxon Mahmudova', 'Робахон Анваровна Махмудова']</t>
+          <t>['Robaxon Anvarovna Maxmudova', 'Robaxon Mahmudova']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Judge']</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1106,12 +1102,12 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['伊尔霍姆·鲁斯塔莫维奇·马赫卡莫夫', 'Махкамов Илхом Рустамович', 'Ilhom Mahkamov', 'Ilhom Rustamovich Mahkamov', 'Илхом Махкамов']</t>
+          <t>['Илхом Махкамов', 'Ilhom Rustamovich Mahkamov', 'Ilhom Mahkamov']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1284,12 +1280,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['ムラート・カマロフ', 'Murat Kallibekovich Kamalov', 'Камалов Мурат Каллибекович', 'Murat Kallimbekovich Kamalov', 'مراد كاليبيكوفيتش كمالوف', 'Murat Kamalov', 'Murod Kallibekovich Kamolov', 'مراد كمالوف', 'Murod Kamolov']</t>
+          <t>['Murat Kallibekovich Kamalov', 'مراد كاليبيكوفيتش كمالوف', 'Murat Kallimbekovich Kamalov', 'Murat Kamalov', 'Murod Kallibekovich Kamolov']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1462,12 +1458,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['مقصوده وارثوا', 'مقصودة فوريسوف', 'مقصوده عزیزوونا وارثوا', 'Варисова Максуда Азизовна', 'Մաքսուդա Վարիսովա', 'Maqsuda Azizovna Vorisova', 'Maqsuda Vorisova', 'Maqsuda Varisova', '马克苏达·瓦里索娃']</t>
+          <t>['مقصوده عزیزوونا وارثوا', 'Maqsuda Azizovna Vorisova', 'Maqsuda Varisova']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1544,7 +1540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dawron Nazarmuhamedow</t>
+          <t>Davron Nazarmuhamedov</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1640,12 +1636,12 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['Dawron Nazarmuhamedow', 'General', 'Davron Nazarmuhamedov']</t>
+          <t>['Davron Nazarmuhamedov', 'General']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1685,7 +1681,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Officer']</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -1810,12 +1806,12 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['Nazir Sobirov', 'Nazir Sabirov', 'Сабіров Назір Нажметдінович', 'Сабиров Назир Нажметдинович']</t>
+          <t>['Nazir Sobirov', 'Nazir Sabirov']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1980,12 +1976,12 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['Хамзаев Дилшод Баймуродович', 'Хамзаєв Ділшод Баймуродович', 'Dilshod Xamzayev']</t>
+          <t>['Dilshod Xamzayev']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -2154,12 +2150,12 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['Ravshanbek Davletovich Qurbonov', 'Ravshanbek Qurbonov', 'Курбанов Равшанбек Давлетович', 'Qurbonov Ravshanbek Davletovich']</t>
+          <t>['Ravshanbek Davletovich Qurbonov', 'Qurbonov Ravshanbek Davletovich']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -2199,7 +2195,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Physician', 'Politician', 'Statesperson']</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -2332,12 +2328,12 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['Шоумаров Гайрат Бахромович', "Shoumarov G'ayrat Baxromovich", 'Gʻayrat Shoumarov']</t>
+          <t>['[Gʻayrat Shoumarov]', "Shoumarov G'ayrat Baxromovich"]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2510,12 +2506,12 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['Bakhtiyor Fazilov', 'بختیار فاضیلوف', 'Baxtiyor Shuhratovich Fozilov', 'Bakhtiyor Fazylov', 'Фазылов Бахтиёр Шухратович', 'Bakhtiyor Shukhratovich Fazilov', 'Baxtiyor Fozilov']</t>
+          <t>['Bakhtiyor Shukhratovich Fazilov', 'Bakhtiyor Fazilov', 'Baxtiyor Shuhratovich Fozilov']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2592,7 +2588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Navruz Ibodullayevich Rizayev</t>
+          <t>Navroz Rizaev</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -2684,12 +2680,12 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['Ризаев Навруз Ибодуллаевич', 'Navruz Ibodullayevich Rizayev', 'Navroʻz Rizayev', 'Navroz Rizaev']</t>
+          <t>['[Navroʻz Rizayev]', 'Navroz Rizaev', 'Navruz Ibodullayevich Rizayev']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2862,12 +2858,12 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name']</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['Risboy Joʻrayev', 'Джураев Рисбай Хайдарович']</t>
+          <t>['[Risboy Joʻrayev]']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -3040,12 +3036,12 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['Дільнозахон Каттахонова', 'دلنازهخان کتهخانوا', '딜노자혼 카타호노바', 'ديلنوزاخون كاتاخونوفا', 'Дилнозахон Каттахонова', 'Dilnozaxon Kattaxanova', 'Դիլնոզախոն Կատախոնովա', 'ディルノザホン・カッタホノヴァ', 'Dilnozaxon Kattaxonova']</t>
+          <t>['Dilnozaxon Kattaxanova']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -3085,7 +3081,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3218,12 +3214,12 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['Zakir', 'زوكير الماتوف', 'Zokir Almatov', 'Алматов Закир Алматович', 'Закир Алматович Алматов', 'ザキルジョン・アルマトフ']</t>
+          <t>['Алматов Закир Алматович', 'Zokir Almatov', 'Zakir']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -3263,7 +3259,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -3352,7 +3348,11 @@
           <t>Individual</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/Zulayho_Mahkamova_2026.jpg</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>uz_gen</t>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['Զուլայխո Մախկամովա', 'Zulayho Mahkamova', 'Зулайхо Махкамова']</t>
+          <t>['Zulayho Mahkamova']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Juraev Rustam Mirzaevich</t>
+          <t>Rustam Jorayev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name']</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['Джураев Рустам Мирзаевич', 'Rustam Joʻrayev']</t>
+          <t>['[Rustam Joʻrayev]']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -3657,7 +3657,11 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Uzbek Politician</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>0</v>
@@ -3727,17 +3731,17 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Uzbekistan']</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['Мирзаев Руслан Эркинович', 'Ruslan Mirzaev', '米尔扎耶夫·鲁斯兰·埃尔基诺维奇']</t>
+          <t>['Ruslan Mirzaev']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3777,22 +3781,22 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Minister Of Defense']</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2005-11-18']</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2008-09-17']</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -3906,12 +3910,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['Odil Abdurakhmanov', 'ओडिल अब्दुरखमानोव्ह', 'Odil Abdurahmonov', 'عادل عبد الرحمانوف', 'Одил Каландарович Абдурахманов']</t>
+          <t>['Odil Abdurahmonov']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -4080,12 +4084,12 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['Aziz Voitov', 'Воитов Азиз Ботирович', 'Азиз Воитов']</t>
+          <t>['Азиз Воитов', 'Aziz Voitov']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -4258,12 +4262,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['Jurabek Mirzamakhmudov', 'Джурабек Турсунпулатович Мирзамахмудов', 'Мирзамахмудов Джурабек', 'Mirzamahmudov Joʻrabek Tursunpoʻlatovich', 'Мирзамахмудов Журабек', 'Zhurabek Mirzamakhmudov', 'Jurabek Mirzamahmudov']</t>
+          <t>['Джурабек Турсунпулатович Мирзамахмудов', 'Мирзамахмудов Джурабек', 'Jurabek Mirzamahmudov', 'Mirzamahmudov Joʻrabek Tursunpoʻlatovich', 'Jurabek Mirzamakhmudov']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -4432,12 +4436,12 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['Акбар Ташкулов', 'Toshqulov Akbar', 'Ташкулов Акбар Джурабаевич', 'Akbar Tashkulov', 'Akbar Toshqulov', 'Ташкулов Акбар Джурабаевич Акбар Ташкулов', 'Toshqulov Akbar Joraboyevich']</t>
+          <t>['Ташкулов Акбар Джурабаевич Акбар Ташкулов', 'Akbar Tashkulov', 'Toshqulov Akbar Joraboyevich', 'Toshqulov Akbar', 'Акбар Ташкулов']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -4606,12 +4610,12 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['Салихбаев Анвар Саидович', 'Anvar Salihbayev']</t>
+          <t>['Anvar Salihbayev']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -4651,7 +4655,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Military Personnel', 'Politician']</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -4780,12 +4784,12 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['Maxsetbaev Polat Maxsetbay Uli', 'Polat Maxsetbaev', 'Махсетбаэв Пўлат Махсетбай ўғли', 'Maxsetbaev Poʻlat Maxsetbay oʻgʻli', 'Polat Maxsetbayev', "Po'lat Maxsetbaev", 'Пўлат Махсетбаэв', 'Полат Махсетбаев']</t>
+          <t>['Maxsetbaev Polat Maxsetbay Uli', 'Polat Maxsetbaev', 'Polat Maxsetbayev', 'Махсетбаэв Пўлат Махсетбай ўғли', 'Maxsetbaev Poʻlat Maxsetbay oʻgʻli']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -4825,7 +4829,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -4958,12 +4962,12 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['Хасанбой Бурханов', 'Бурханов Хасанбой', 'Hasanboy Burxonov']</t>
+          <t>['Бурханов Хасанбой', 'Hasanboy Burxonov']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -5003,7 +5007,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -5132,12 +5136,12 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['Умурзаков Шавкат Буранович', 'Szawkat Umurzakov', 'Shavkat Umurzoqov']</t>
+          <t>['Shavkat Umurzoqov']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -5355,7 +5359,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Jurist', 'Politician']</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -5533,7 +5537,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -5662,12 +5666,12 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['Камалиддин Бабаев', 'Kamaliddin Babaev', 'Komoliddin Babayev']</t>
+          <t>['Kamaliddin Babaev']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -5707,7 +5711,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -6014,12 +6018,12 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['Bekhzod Akhmedov', 'Bekhzod V Akhmedov', 'Бехзод Баходирович Ахмедов', 'Ахмедов Бехзод Баходирович', 'بيخزود اخميدوڤ', 'Bechsod Achmedow', 'Bekhzod Bakhodirovich Akhmedov', 'بهزاد احمدوف']</t>
+          <t>['Бехзод Баходирович Ахмедов', 'Bechsod Achmedow', 'Bekhzod Bakhodirovich Akhmedov']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -6059,7 +6063,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Chief Executive Officer', 'Entrepreneur']</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -6096,7 +6100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anvar Otahojayev</t>
+          <t>Otakhodjayev Anvar Khojakhanovich</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -6193,7 +6197,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['Anvar Otaxoʻjayev', 'Otaxoʻdjayev Anvar Xoʻjaxanovich', 'Otaxoʻjayev Anvar Xoʻjaxanovich']</t>
+          <t>['Otaxoʻdjayev Anvar Xoʻjaxanovich', 'Otaxoʻjayev Anvar Xoʻjaxanovich', 'Anvar Otaxoʻjayev']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -6279,7 +6283,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Uzbekistani Businessperson</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Qarshi</t>
@@ -6357,17 +6365,17 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Uzbekistan']</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>['Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['Sanjar Bekov']</t>
+          <t>['Sanjar Bekov', 'Sanjar Bekov Bekov Sanjar Sanjar Bekov Bahtiyor Ogli Bekov Sanjar Bahtiyor Ogli', 'Sanjar Bekov Bahtiyor Ogli']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -6407,7 +6415,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -6581,7 +6589,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Pedagogue', 'Politician']</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -6710,12 +6718,12 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['Усманов Рахмонбек Джахонгирович', 'Rahmonqul Jahongirovich Usmonov', 'Rahmonbek Usmonov', 'Раҳмонқул Жаҳонгирович Усмонов', 'Рахмонбек Усманов', 'Рахмонбек Джахонгирович Усманов', 'Rahmonbek Usmanov']</t>
+          <t>['Rahmonqul Jahongirovich Usmonov', 'Раҳмонқул Жаҳонгирович Усмонов', 'Рахмонбек Усманов', 'Усманов Рахмонбек Джахонгирович', 'Rahmonbek Usmanov']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -6755,7 +6763,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -6792,7 +6800,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gulomov Saidahror Saidaxmedovich</t>
+          <t>Saidahror Gulomov</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -6888,12 +6896,12 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['Гулямов Саидахрор Саидахмедович', "G'ulomov Saidahror Saidaxmedovich", "Saidahror G'ulomov", 'Саидахрор Гулямов', '사이다흐로르 굴리야모프', 'Саидахрор Саидахмедович Гулямов']</t>
+          <t>["[Saidahror G'ulomov]", 'Саидахрор Гулямов', "G'ulomov Saidahror Saidaxmedovich", 'Гулямов Саидахрор Саидахмедович']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -6933,7 +6941,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -7099,7 +7107,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -7145,7 +7153,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Tashkent</t>
@@ -7219,17 +7231,17 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Uzbekistan']</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['Жавлон Камолов', 'Javlon Kamolov']</t>
+          <t>['Javlon Kamolov']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -7269,7 +7281,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -7315,7 +7327,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Uzbekistani Politician</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>0</v>
@@ -7389,7 +7405,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Uzbekistan']</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -7399,7 +7415,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['Тулкин Сайфуллаевич Абдусаттаров', 'Toʻlqin Abdusattarov']</t>
+          <t>['Toʻlqin Sayfullayevich Abdusattarov', '[Toʻlqin Abdusattarov]']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -7439,7 +7455,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -7568,12 +7584,12 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['دلوروم یلدوشیوا', 'Dilorom Yuldosheva', 'Dilorom Yoʻldosheva', 'Dilorom Yuldasheva']</t>
+          <t>['[Dilorom Yoʻldosheva]', 'Dilorom Yoʻldosheva', 'Dilorom Yuldasheva']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -7613,7 +7629,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson', 'Seamstress']</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -7824,7 +7840,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Farhodjon Ortiqovich Shermatov</t>
+          <t>Farhodjon Shermatov</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -7908,12 +7924,12 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['Farhodjon Ortiqovich Shermatov', 'Фарҳоджон Шерматов', 'Farhodjon Shermatov']</t>
+          <t>['Farhodjon Shermatov', 'Farhodjon Ortiqovich Shermatov', 'Фарҳоджон Шерматов']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -7953,7 +7969,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Officer', 'Military Personnel']</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -8086,12 +8102,12 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['Ташпулатов Азиз Анварович', 'Aziz Anvarovich Toshpulatov', 'Aziz Toshpoʻlatov']</t>
+          <t>['[Aziz Toshpoʻlatov]', 'Aziz Anvarovich Toshpulatov']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -8256,12 +8272,12 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['Улугбек Миррустамович Шадманов', 'Ulugbek Shadmanov', 'الغبیک شادمانوف', 'Шадманов Улугбек', 'Улугбек Шадманов']</t>
+          <t>['Ulugbek Shadmanov', 'Шадманов Улугбек', 'Улугбек Шадманов']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -8301,7 +8317,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -8338,7 +8354,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Merey Amanbayeva</t>
+          <t>Merey Erali Qizi Amanbayeva</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -8430,12 +8446,12 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['Merey Amanbayeva', 'Мерей Ералы қызы Аманбаева', 'Merey Erali Qizi Amanbayeva']</t>
+          <t>['Merey Erali Qizi Amanbayeva', 'Merey Amanbayeva', 'Мерей Ералы қызы Аманбаева']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -8475,7 +8491,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Manager', 'Politician', 'Teacher']</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -8596,12 +8612,12 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['Shuhrat Sobirov Oʻrinboyevich', 'Sobirov Shuhrat Oʻrinboyevich', 'Shuhrat Sobirov']</t>
+          <t>['Shuhrat Sobirov', 'Shuhrat Sobirov Oʻrinboyevich', 'Sobirov Shuhrat Oʻrinboyevich']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -8641,7 +8657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Officer', 'Military Personnel']</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
@@ -8940,12 +8956,12 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['Отабек Махкамов', 'Otabek Mahkamov']</t>
+          <t>['Otabek Mahkamov']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -8985,7 +9001,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -9022,7 +9038,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sanzhar Hamidullaev</t>
+          <t>Sanjar Xamidullayev</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -9114,12 +9130,12 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['Хамидуллаев Санжар Асатуллаевич', 'Sanzhar Hamidullaev', 'Sanjar Hamidullaev', 'Sanjar Xamidullayev']</t>
+          <t>['Sanjar Xamidullayev', 'Sanjar Hamidullaev', 'Sanzhar Hamidullaev']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -9292,12 +9308,12 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['Γιουλντούζ Ουσμάνοβα', 'یولدوز عثمانوا', 'Усмонова Юлдуз Урайимохуновна', 'Юлдуз Усмонова', 'Γιουλντούζ Ουραϊμοχούνοβνα Ουσμάνοβα', 'Yıldız Usmanova', 'Yulduz Urayimohunovna Usmonova', 'Yulduz Usmonova', 'Γιουλντούζ Ιμπραγκίμοβνα Ουσμάνοβα', 'Усмонова Юлдуз', 'Усмонова', 'Yulduz Usmanova', 'Usmanova', 'Yıldız Usmonova', 'Yulduz Urayimohunovna Usmanova', 'Julduz Usmonova', 'Юлдуз Урайимохуновна Усманова', 'Усманова Юлдуз Урайимохуновна', 'Usmonova', 'Յուլդուզ Ուսմանովա', 'عثمانوا', '율드 우스모노바', '尤杜茲·烏絲莫諾娃', '尤爾杜茲·烏斯莫諾娃', 'Yulduz', 'یلدوز عثمانوا', 'Юлдуз Усманова', 'Yulduz Oʻrayimoxunovna Usmonova', 'ユルドゥズ・ウスマノヴァ', 'Юлдуз Урайимохуновна Усмонова']</t>
+          <t>['Yıldız Usmonova', 'Γιουλντούζ Ιμπραγκίμοβνα Ουσμάνοβα', 'Yulduz Oʻrayimoxunovna Usmonova', 'Yulduz Usmonova', 'عثمانوا', 'Usmonova', 'Yulduz Urayimohunovna Usmonova', 'Yulduz Urayimohunovna Usmanova', 'Усмонова', 'Julduz Usmonova', 'Усмонова Юлдуз Урайимохуновна', 'Yıldız Usmanova', 'Юлдуз Урайимохуновна Усмонова', 'Усмонова Юлдуз', 'Γιουλντούζ Ουραϊμοχούνοβνα Ουσμάνοβα', 'Yulduz Usmanova', 'Юлдуз Урайимохуновна Усманова', 'Усманова Юлдуз Урайимохуновна', 'Юлдуз Усмонова', 'Usmanova', 'Yulduz']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -9337,7 +9353,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Composer', 'Film Actor', 'Musician', 'Politician', 'Singer', 'Singer-Songwriter']</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -9357,12 +9373,12 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>['Partner', 'Child']</t>
+          <t>['Child', 'Partner']</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>['UZ-GEN-IH-6G5P2-RCA-1', 'UZ-GEN-NU-DE5TE-RCA-1']</t>
+          <t>['UZ-GEN-NU-7FW1K-RCA-1', 'UZ-GEN-IH-0IVDH-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9482,12 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['Махмудова Шахло Насімовна', '샥슬로 막스무도바', 'شهلا محمودوا', 'Махмудова Шахло Насимовна', 'Shahlo Mahmudova']</t>
+          <t>['Shahlo Mahmudova']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -9644,12 +9660,12 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['Комил Алламжонов', 'Komil Allamzhonov', 'Komil Ismoilovič Allamžonov', 'Комил Исмоилович Алламжонов', 'كوميل اللامجونوف', 'Komil Ismoilovich Allamjonov', 'Komil Allamžonov', 'Komil Allamjonov']</t>
+          <t>['Комил Исмоилович Алламжонов', 'Komil Ismoilovič Allamžonov', 'Komil Allamjonov', 'Komil Ismoilovich Allamjonov', 'Komil Allamzhonov']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -9689,7 +9705,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Journalist', 'Politician', 'Statesperson']</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
@@ -9818,12 +9834,12 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['Хатамжон Абдурахманович Кетмонов', 'Кетмонов Хотамжон Абдурахмонович', 'Hotamjon Ketmonov', '哈塔姆江·克塔曼諾夫', 'Hotamjon Abdurahmonovich Ketmonov', 'Hatemcan Ketmanov', '哈塔姆江·克塔曼诺夫', 'Hatemcan Abdurrahmanoviç Ketmanov', 'Хотамжон Абдурахмонович Кетмонов', 'Chotamschon Abdurachmanowitsch Ketmonow', 'Chotamschon Ketmonow', 'Хотамжон Кетмонов']</t>
+          <t>['Хатамжон Абдурахманович Кетмонов', 'Хотамжон Кетмонов', 'Hatemcan Abdurrahmanoviç Ketmanov', 'Кетмонов Хотамжон Абдурахмонович', 'Chotamschon Ketmonow', 'Hotamjon Abdurahmonovich Ketmonov', 'Chotamschon Abdurachmanowitsch Ketmonow']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -9863,7 +9879,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Language Teacher', 'Politician']</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -9996,12 +10012,12 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['אלימזאן טוחטחונוב', 'Тахтахунов Алимжан Урсулович', '알림잔 투르수노비치 토흐타후노프', 'Alimzjan Tursunovitj Tochtachunov', 'Alimzhan Tokhtakhounov', 'Алимжан Тохтатунов', 'Алимжан Урсулович Тахтахунов', 'Alimzhan Tokhtakhunov', 'Alimzjan Tochtachunov', 'عالمجان تختهخانوف', 'Тохтахунов Алымжан Турсунович', 'اليمزهان توختاخونوڤ', 'Olimjon Toʻxtaoxunov', 'Тохтахунов', 'Alimzjan Tursunovitsj Tokhtakhunov', 'Алимжан Турсунович Тохтахунов', 'Тохтахунов Алимжан Турсунович', 'Тахтахунов Алимжан', 'Алимжан Тохтахунов', 'عالمجان تورسونویچ تختهخانوف', 'Тохтахунов Алимжан', 'Alimzjan Tokhtakhunov', 'アリムジャン・トフマフノフ', 'Алимжан Тахтахунов', 'Alimzhan Tursunovich Tokhtakhounov', '알림잔 토흐타후노프', 'Tochtachunov', 'Тайванчик', 'Тахтахунов', '阿里木江·吐尔逊诺维奇·托合塔洪诺夫', 'Тахтахунов Алимжан Турсунович']</t>
+          <t>['Алимжан Тохтатунов', 'Алимжан Турсунович Тохтахунов', 'عالمجان تورسونویچ تختهخانوف', 'Алимжан Тахтахунов', 'Тахтахунов', 'Alimzjan Tursunovitsj Tokhtakhunov', 'Тахтахунов Алимжан Урсулович', 'Алимжан Урсулович Тахтахунов', 'Тохтахунов', 'Alimzhan Tokhtakhounov', 'Тохтахунов Алимжан', 'Alimzhan Tursunovich Tokhtakhounov', 'Tochtachunov', 'Алимжан Тохтахунов', 'Тахтахунов Алимжан', 'Тохтахунов Алымжан Турсунович', 'Тохтахунов Алимжан Турсунович', 'Тахтахунов Алимжан Турсунович', 'Тайванчик', '알림잔 투르수노비치 토흐타후노프', 'Alimzjan Tursunovitj Tochtachunov']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -10041,7 +10057,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Actor', 'Athlete', 'Businessperson', 'Entrepreneur']</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -10170,12 +10186,12 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['Adham Ahmadboyev', 'Ахмедбаев Адхам Акрамович', 'ادهم احمد بايف', 'Adham Ahmedbaev', 'ادهم احمدبائف']</t>
+          <t>['Adham Ahmadboyev']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -10215,7 +10231,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Personnel', 'Politician']</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -10348,12 +10364,12 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['Rustam Sadykovich Asimov', 'Rustam Sodiqovich Azimov', 'Азімов Рустам Содікович', 'Rustam Azimov', 'Азимов Рустам Содикович', 'Rustam Asimow', 'رستم عظیموف', 'Rustam Atsimov', 'ルスタム・アジモフ']</t>
+          <t>['Rustam Sadykovich Asimov', 'Rustam Sodiqovich Azimov', 'Rustam Asimow', 'Rustam Atsimov']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -10403,12 +10419,12 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>['2005-02-04', '2005-11-22', '1998-01-01']</t>
+          <t>['2005-02-04', '1998-01-01', '2005-11-22']</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>['2017-06-06', '2016-12-15', '2000-11-08']</t>
+          <t>['2017-06-06', '2000-11-08', '2016-12-15']</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -10526,12 +10542,12 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['ნიგმატილა იულდაშევი', 'Nigmatilla Tulkinowitsch Juldaschew', '尼格马季拉·尤尔多舍夫', 'Nigʻmatilla Yoʻldoshev', 'Nigmatilla Tulkinovich Yuldashev', 'Niqmatilla Yoldaşov', '尼格瑪迪亞·尤爾達舍夫', 'Нігмаціла Тулкінавіч Юлдашаў', 'Нігматілла Юлдашев', 'ニグマティッラ・ユルダシェフ', 'Nigʻmatilla Toʻlqinovich Yoʻldoshev', 'Nigmatilla Juldasjev', 'Нигматилла Юлдашев', 'Неъматулло Юлдошев', 'Нігматыла Юлдашаў', 'Nimetullah Yoldaşev', 'ניגמטילה יולדאשב', 'निगमतिल्ला युल्दाशेव', 'Nigmatilla Juldaschew', "Nig'matilla To'lqinovich Yo'ldoshev", 'Nimetullah Tulkinoğlu Yoldaşev', 'Nigmatilla Yuldașev', 'Нығметолла Юлдашев', 'Нигматилла Тулкинович Юлдашев', '尼格馬季拉·尤爾多舍夫', '니그마틸라 욜도셰프', 'Ниғматилла Тулкинович Юлдашев', 'Nigmatilla Yuldashev', 'نعمه الله يولداشيف', 'Nigmatilla Tolqinovich Yoldoshev', 'Нығметолла Толқынұлы Юлдашев', 'نعمتالله یولداشف', 'Nigmatilla Yoldoshev', 'Nigmatilla Ioldoshev', 'نيغماتولا يولداشيف', 'نعمة الله يولداشيف', 'Նիգմատիլա Յուլդոշև', 'ニグマティラ・ユルダシェフ', 'Юлдашев Нығметолла Толқынұлы', 'นึฆมาตึลลา โยลดอชิฟ', 'Юлдашев Нигматилла Тулкинович']</t>
+          <t>["Nig'matilla To'lqinovich Yo'ldoshev", 'Nigmatilla Tolqinovich Yoldoshev', 'Нығметолла Юлдашев', 'Nigmatilla Tulkinowitsch Juldaschew', 'Юлдашев Нигматилла Тулкинович', 'نيغماتولا يولداشيف', '尼格瑪迪亞·尤爾達舍夫', 'Нигматилла Юлдашев', 'Nigʻmatilla Toʻlqinovich Yoʻldoshev', 'Nimetullah Tulkinoğlu Yoldaşev', 'Юлдашев Нығметолла Толқынұлы', 'Ниғматилла Тулкинович Юлдашев', 'Nigmatilla Ioldoshev', 'Nigmatilla Tulkinovich Yuldashev', 'ニグマティッラ・ユルダシェフ']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -10704,12 +10720,12 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['Дилором Тошмуҳамедова', 'Diloram Gafurjanovna Tashmukhamedova', 'Dilorom Gʻofurjonovna Toshmuhamedova', '딜로람 타슈무하메도바', 'Toshmuhamedova Dilorom Gofurjonovna', 'Ташмухамедова Дилором Гафурджановна', 'Diloram Tashmukhamedova', '迪洛罗姆·塔什穆罕梅多娃', 'دلارام تاشمحمدوا', 'ديلورام تاشموخاميدوفا', 'Dilorom Toshmuhamedova', 'Dilorom Taschmukhamedova', 'Дилорам Ғафурджановна Ташмухамедова', '迪洛羅姆·塔什穆罕梅多娃', 'Dilarem Gafurcanovna Taşmuhammedova']</t>
+          <t>['[Dilarem Gafurcanovna Taşmuhammedova]', 'Dilorom Gʻofurjonovna Toshmuhamedova', 'Diloram Gafurjanovna Tashmukhamedova', 'Toshmuhamedova Dilorom Gofurjonovna']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -10749,7 +10765,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
@@ -10882,12 +10898,12 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['Erkinjon Turdimov', 'Erkinjan Turdimov', 'Эркинжон Окбутаевич Турдимов', 'Эркинжон Турдимов']</t>
+          <t>['Erkinjan Turdimov', 'Erkinjon Turdimov']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -10927,7 +10943,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
@@ -11060,12 +11076,12 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['Kabul Berdiyev', 'Кабул Раимович Бердиев', 'كوبول بيرديڤ', 'カブール・ベルディエフ', 'Qobul Berdiyev', 'Qobul Raimowitch Berdijew', 'Kabul Raimoğlu Berdiyev', 'Qobul Berdijew', 'Qobul Raimovich Berdiev']</t>
+          <t>['Qobul Raimowitch Berdijew', 'Qobul Raimovich Berdiev', 'Kabul Raimoğlu Berdiyev', 'Kabul Berdiyev']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -11238,12 +11254,12 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['Ilgizar Matyoqubovich Sobirov', 'Собиров Илгизар Матякубович', 'Ilgizar Sobirov']</t>
+          <t>['Ilgizar Matyoqubovich Sobirov', 'Ilgizar Sobirov']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -11283,7 +11299,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -11412,12 +11428,12 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['Ikhtiyor Bakhtiyorovich Abdullayev', 'İhtiyar Abdullayev', 'Абдуллаев Ихтиёр Бахтиёрович', 'Ixtiyor Baxtiyorovich Abdullayev', 'اختیار عبداللهاف', 'Ikhtiyor Abdullayev', 'Ixtiyor Abdullayev', 'Իխտիոր Աբդուլաև', 'İhtiyar Bahtiyaroviç Abdullayev']</t>
+          <t>['Ikhtiyor Abdullayev', 'Ixtiyor Baxtiyorovich Abdullayev', 'İhtiyar Bahtiyaroviç Abdullayev', 'Ikhtiyor Bakhtiyorovich Abdullayev']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -11590,12 +11606,12 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['سوديك سافويڤ', 'Содиқ Солиҳович Сафоев', 'Sodiq Solihovič Safoev', 'Садык Салихович Сафаев', 'Sadyk Safaev', 'Sadik Safaiev', 'Sodiq Safoyev', 'Sadyk Safayev', 'Sadyk Salichovič Safaev', 'Sodiq Solihovich Safoyev', 'Сафаев Садык Салихович', 'Sadyk Safajew', 'Safoyev', 'Sodiq Safoev', 'サディク・サファエフ', 'صدیق صفایف']</t>
+          <t>['Содиқ Солиҳович Сафоев', 'Садык Салихович Сафаев', 'Sodiq Solihovič Safoev', 'Sadyk Salichovič Safaev', 'Sodiq Safoev', 'Sadyk Safajew', 'Sadik Safaiev', 'Sadyk Safaev', 'Sadyk Safayev', 'Safoyev', 'Sodiq Solihovich Safoyev']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -11635,7 +11651,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician', 'Sports Executive']</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -11764,12 +11780,12 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['Saidullo Parxodbekovich Abdullaev', 'Abdullaev Saidullo Parxodbekovich', 'Saidullo Abdullaev', 'Saydullo Abdullayev']</t>
+          <t>['Saidullo Abdullaev', 'Abdullaev Saidullo Parxodbekovich']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -11809,7 +11825,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson']</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -11938,12 +11954,12 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['Саидова Галина Каримовна', 'Galina Saidova', 'Galina Karimovna Saidova']</t>
+          <t>['Galina Karimovna Saidova', 'Galina Saidova']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -11983,7 +11999,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
@@ -12116,12 +12132,12 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['Ікрамов Музраф Муборакходжайович', 'Muzrob Ikromov', 'Muzraf Ikramov', 'Икрамов Музраф Муборакходжаевич']</t>
+          <t>['Muzraf Ikramov']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -12161,7 +12177,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
@@ -12290,12 +12306,12 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['Tursinxon Xudayberganov', 'Tursinkhon Khudayberganov', 'Турсинхан Худайбергенов', 'Тұрсынхан Айдарұлы Құдайбергенов', 'Худайбергенов Турсинхан Айдарович', 'Tursinkhan Khudaibergenov', 'Tursinxon Xudoyberganov']</t>
+          <t>['Tursinkhon Khudayberganov', 'Турсинхан Худайбергенов', 'Тұрсынхан Айдарұлы Құдайбергенов', 'Tursinkhan Khudaibergenov']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -12464,12 +12480,12 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['Anvar Alimov', 'Anvar Alimov Barnoevich', 'Алимов Анвар Барноевич']</t>
+          <t>['Anvar Alimov']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -12509,7 +12525,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
@@ -12646,12 +12662,12 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['Alina Kabajewa', 'Αλίνα Καμπάεβα', 'Alīna Kabajeva', 'Alina Kabayeva', '알리나 카바예바', 'Алина Қабаева', 'อลินา คาบาเอวา', 'Кабаева А', 'Қабаева Алина Маратқызы', 'Қабаева Алина', 'Қабаева', 'ალინა კაბაევა', 'Әлинә Кабаева', 'アリーナ・カバエワ', 'ألينا كاباييفا', 'Алина Маратовна Кабаева', 'الىينا قابايەۆا', 'Кабаева Алина', 'Älinä Marat qızı Qabayeva', 'Alina Maratowna Kabajewa', 'الينا كاباييفا', 'آلینا کابیوا', 'Кабаева', 'Alina Kabáyeva', 'Alina Kabaeva', 'Alina Martovna Kabajeva', 'Кабаева А М', 'Alina Kabajeva', 'อาลีนา คาบาเอวา', 'Alina Qabayeva', 'Alina Kabaieva', 'Кабаева Алина Маратовна', 'Eline Kabayeva', 'Alina Kabajevová', 'Алина Маратқызы Қабаева', 'Алина Марат ҡыҙы Ҡабаева', 'Кабаєва Аліна Маратівна', 'Ալինա Կաբաևա', '卡巴耶娃', 'আলিনা মারাতোভনা কাবায়েভা', 'Alina Maratovna Kabaïeva', 'Алина Кабаева', 'Аліна Кабаєва', 'אלינה קבייבה', 'Alina Maratovna Kabaeva', 'Әлинә Марат кызы Кабаева', 'Алина Ҡабаева', 'Кабаєва Аліна', 'الینا کابیوا', 'Kabajevová', 'Alina Maratovna Kabaieva', '阿林娜·卡巴耶娃', 'Aļina Kabajeva', 'Eline Muratkızı Kabayeva', 'Alina Kabaïeva', 'আলিনা কাবায়েভা', 'Аліна Маратаўна Кабаева', 'Alina Maratovna Kabajeva', 'Аліна Кабаева', 'Ҡабаева Алина Марат ҡыҙы', 'Alïna Qabayeva', 'Alina Marátovna Kabáyeva', 'Alina Maratovna Kabayeva', 'Kabajewa']</t>
+          <t>['Қабаева Алина', 'Alina Kabajewa', 'Кабаева Алина', 'Алина Марат ҡыҙы Ҡабаева', 'Kabajewa', 'Қабаева', 'Alina Kabaieva', 'Eline Muratkızı Kabayeva', 'Alina Kabaeva', 'Alina Maratowna Kabajewa', 'อาลีนา คาบาเอวา', 'Alina Kabajeva', 'Kabajevová', 'Кабаева Алина Маратовна', 'Alina Maratovna Kabaïeva', 'Кабаєва Аліна', 'Alina Qabayeva', 'Аліна Кабаєва', 'Кабаева А М', 'Alina Maratovna Kabajeva', 'Alina Kabayeva', 'อลินา คาบาเอวา', 'Қабаева Алина Маратқызы', 'Alina Marátovna Kabáyeva', 'Alīna Kabajeva', 'Аліна Кабаева', 'Кабаева А', 'Алина Ҡабаева', 'আলিনা মারাতোভনা কাবায়েভা', 'Алина Маратовна Кабаева', 'Кабаева', '卡巴耶娃', 'Alina Maratovna Kabaieva', 'Älinä Marat qızı Qabayeva', 'Алина Кабаева', 'Alina Maratovna Kabaeva', 'Alina Martovna Kabajeva', 'Алина Қабаева', 'Әлинә Марат кызы Кабаева', 'Alina Maratovna Kabayeva']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -12691,7 +12707,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>['Film Actor', 'Model', 'Politician', 'Rhythmic Gymnast']</t>
+          <t>['Athlete', 'Film Actor', 'Model', 'Politician', 'Rhythmic Gymnast']</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
@@ -12711,12 +12727,12 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>['Mother', 'Child', 'Child']</t>
+          <t>['Child', 'Child', 'Mother']</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>['UZ-GEN-LK-SO4AK-RCA-1', 'UZ-GEN-IP-W3VCD-RCA-1', 'UZ-GEN-VPJ-KXHV0-RCA-1']</t>
+          <t>['UZ-GEN-IP-4LXIG-RCA-1', 'UZ-GEN-VPJ-C1JFM-RCA-1', 'UZ-GEN-LK-1HSLO-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -12824,12 +12840,12 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['Tatyana Kerimova', 'Тетяна Акбарівна Каримова', 'Tatyana Akbarovna Karimova', 'Таццяна Акбараўна Карымава', '塔季揚娜·卡里莫娃', 'تاتيانا كاريموڤا', 'Татьяна Каримова', 'Tatiana Karimova', 'Tatjana Akbarowna Karimowa', 'ტატიანა ქარიმოვა', 'タチヤーナ・カリモヴァ', 'Tatyana Karimova', 'טטיאנה קרימובה', 'تاتیانا کریمووا', 'تاتيانا كريموفا', 'Tatyana Ekberovna Kerimova', 'Татьяна Акбаровна Каримова', 'Татяна Каримова', '타치야나 카리모바', 'Каримова Татьяна Акбаровна', 'Татьяна Акбарқызы Кәрімова', 'Tatjana Karimowa']</t>
+          <t>['Tatyana Akbarovna Karimova', 'Каримова Татьяна Акбаровна', 'Tatjana Karimowa', 'Татьяна Акбаровна Каримова', 'Tatjana Akbarowna Karimowa', 'Татьяна Каримова', 'Tatyana Ekberovna Kerimova', 'Tatiana Karimova']</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -12889,12 +12905,12 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>['Partner', 'Child', 'Child']</t>
+          <t>['Child', 'Child', 'Partner']</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>['UZ-GEN-IK-2A3V8-RCA-1', 'UZ-GEN-GK-UYW9Q-RCA-1', 'UZ-GEN-LKT-E761N-RCA-1']</t>
+          <t>['UZ-GEN-GK-75XA0-RCA-1', 'UZ-GEN-LKT-7C98Z-RCA-1', 'UZ-GEN-IK-5A8DA-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -13002,12 +13018,12 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['عبداللہ عاریپوف', 'Абдулла Арипов', '阿里波夫', 'Abdulla Nigmatovitj Aripov', 'アブドゥッラー・アリポフ', 'Абдулла Орипов', 'Абдула Арипов', 'アブドゥラ・アリポフ', 'Арипов Абдулла Нигматович', 'עבדולה אריפוב', 'อับดุลลา อารีปัฟ', 'عبدالله عارفوف', '阿卜杜拉·阿里波夫', 'Abdulla Nigmatowitsch Aripow', 'Абдулла Аріпов', 'Abdulla Oripov', 'Abdulla Nigmatovich Aripov', 'Абдулла Нигматович Арипов', 'Abdulla Aripow', 'Абдулла Әріпов', 'Абдулла Нығматұлы Әріпов', 'Αμπντουλά Aρίποφ', 'Абдулла Ниғматұлы Әріпов', '압둘라 아리포프', 'عبد الله نجماتوفيتش اريبوف', 'Арипов Абдулла Ниғмәт улы', 'Abdulla Nigʻmatovich Oripov', 'Абдула Арыпаў', 'Abdulla Aripov', 'عبد الله عارفوف', 'Աբդուլա Արիպով', 'አብዱላ ኦርፖቭ', 'Абдулла Ниғматович Арипов', 'Абдулла Нигъмәт улы Арипов', 'Абдулло Орипов']</t>
+          <t>['Abdulla Oripov', 'Abdulla Nigmatovitj Aripov', 'Абдулла Орипов', 'Абдулла Нигъмәт улы Арипов', 'Арипов Абдулла Нигматович', 'アブドゥラ・アリポフ', 'Абдулла Нығматұлы Әріпов', 'Abdulla Aripow', 'Abdulla Nigmatowitsch Aripow', 'Abdulla Nigmatovich Aripov', 'Abdulla Aripov', '阿里波夫', 'Абдулла Арипов', 'Абдулла Ниғматович Арипов', 'Абдулла Әріпов']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -13180,12 +13196,12 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['Икрамов Адхам Ильхамович', 'Адхам Икрамов', 'آدخام اکراموف', 'Adxam Ilxamovich Ikramov', 'Ікрамов Адхам Ільхамович', 'Adxam Ikramov', 'Adham Ikromov']</t>
+          <t>['Адхам Икрамов', 'Adxam Ilxamovich Ikramov', 'Adham Ikromov']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -13354,12 +13370,12 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>['Alisher Shodmonov', 'Алишер Қаюмович Шадманов / Alisher Qayumovich Shadmanov', 'Алишер Каюмович Шадманов']</t>
+          <t>['Алишер Қаюмович Шадманов / Alisher Qayumovich Shadmanov', 'Alisher Shodmonov']</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -13573,7 +13589,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -13706,12 +13722,12 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['Nurdinjon Ismoilov', 'Nuriddin Ismoilov', 'Исмоилов Нурдинжон Муйдинханович', 'نورالدینجان اسماعیلاف', 'Исмоилов Нурдинжон', 'Нуриддин Исмоилов', 'Nurdinjon Moʻydinxonovich Ismailov', 'Nuriddin Moʻydinxonovich Ismoilov', 'Нурдинжон Исмоилов', 'ヌーリッディーンジョン・イスマイロフ', 'Nureddincan Muhiddinhanoviç İsmailov', 'Нурдинджон Исмаилов', 'Nuriddinjon Ismailov', 'Nureddincan İsmailov']</t>
+          <t>['Nuriddin Moʻydinxonovich Ismoilov', 'Нурдинджон Исмаилов', 'Nurdinjon Moʻydinxonovich Ismailov', 'Nurdinjon Ismoilov', 'Nureddincan Muhiddinhanoviç İsmailov', 'Исмоилов Нурдинжон', 'Nuriddinjon Ismailov', 'Исмоилов Нурдинжон Муйдинханович', 'Nuriddin Ismoilov']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -13880,12 +13896,12 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['এরকিন খলিলভ', 'Erkin Hamdamovich Halilov', 'Erkin Hamdanovich Khalilov', 'Erkin Hamdanoviç Halilov', 'Erkin Halilov']</t>
+          <t>['Erkin Halilov', 'Erkin Hamdanoviç Halilov', 'Erkin Hamdanovich Khalilov', 'Erkin Hamdamovich Halilov']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -13925,7 +13941,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -14058,12 +14074,12 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['압둘하심 무탈로프', 'Abdülhaşim Mutaloviç Mutalov', 'Абдулҳошим Муталов', 'Муталов Абдулхашим Муталлович', 'Abdulhashim Mutalovich Mutalov', 'Abdulxashim Mutalov', 'Mutalow', 'Абдулхашим Муталович Муталов', 'Abdulxashim Mutalovich Mutalov', 'Абдулһашим Муталов', 'عبدالهاشم موتالوف', 'Abdülhaşim Mutalov', 'アブドゥルハシム・ムタロフ', 'Абдулхашим Муталлович Муталов', 'Abdulxoshim Mutalovich Mutalov', 'Abdulhoshim Mutalov', 'Abdulhashim Mutalov', 'Абдулхашим Муталов', '阿卜杜勒哈希姆·穆塔洛维奇·穆塔洛夫', 'Mutalov']</t>
+          <t>['Abdulxashim Mutalovich Mutalov', 'Муталов Абдулхашим Муталлович', 'Abdulhashim Mutalovich Mutalov', 'Mutalow', 'Abdülhaşim Mutaloviç Mutalov', 'Abdulxoshim Mutalovich Mutalov', 'Abdulhashim Mutalov', 'Abdulxashim Mutalov', 'Mutalov']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -14228,12 +14244,12 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>['Назыров Феруз Гофурович', 'Feruz Nazirov']</t>
+          <t>['Feruz Nazirov']</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -14273,7 +14289,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
@@ -14411,7 +14427,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['Ходжаев Ботир Асадиллаевич', 'Botir Xoʻjayev']</t>
+          <t>['[Botir Xoʻjayev]', 'Botir Xoʻjayev']</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -14451,7 +14467,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
@@ -14584,12 +14600,12 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>['ولادیمیر نوروف', '弗拉基米爾·諾羅夫', 'Vladimir Imanovich Norov', 'Vladimir Norov', '弗拉基米尔·诺罗夫', 'ウラジーミル・ノロフ', 'Norov', 'Vladimir Imomovich Norov', 'Vladimir Imamovich Norov', 'Владимир Норов', 'Wladimir Norow', 'Норов Владимир Имамович', 'Władimir Norow', '弗拉迪米爾·諾羅夫']</t>
+          <t>['Wladimir Norow', 'Vladimir Imanovich Norov', 'Vladimir Imomovich Norov', 'Vladimir Norov', 'Norov', 'Vladimir Imamovich Norov', 'Владимир Норов']</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -14639,12 +14655,12 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>['2022-04-27', '2022-09-09', '2006-07-12']</t>
+          <t>['2006-07-12', '2022-04-27', '2022-09-09']</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>['2022-09-09', '2022-12-30', '2010-12-01']</t>
+          <t>['2010-12-01', '2022-09-09', '2022-12-30']</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14803,7 +14819,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
@@ -14936,12 +14952,12 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>['Бабаджанов Пулат Раззакович', 'Pólat Bobojonov', 'Poʻlat Bobojonov', 'Пулат Бобожонов']</t>
+          <t>['Poʻlat Bobojonov', '[Poʻlat Bobojonov]', 'Пулат Бобожонов']</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -15114,12 +15130,12 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['Abdusalom Azizov', 'Abdusalam Azizow', 'Abdüsselam Azizov', 'Abdussalom Asisow', 'Абдусалом Абдумавлонович Азизов', 'عبد السلام عزيزوف', 'Abdusalom Abdumavlonovich Azizov', 'Abdussalom Abdumawlonowitsch Asisow', 'عبدالسلام عزیزوف', 'Abdüsselam Abdülmevlanoğlu Azizov']</t>
+          <t>['Abdussalom Abdumawlonowitsch Asisow', 'Abdusalom Azizov', 'Abdusalom Abdumavlonovich Azizov', 'Abdussalom Asisow', 'Abdüsselam Abdülmevlanoğlu Azizov', 'Abdusalam Azizow']</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -15292,12 +15308,12 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>['Светлана Ивановна Герасимова', 'Svetlana Gerasimova', 'Герасимова Светлана Ивановна']</t>
+          <t>['Svetlana Gerasimova', 'Светлана Ивановна Герасимова']</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -15337,7 +15353,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
@@ -15374,7 +15390,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ismoil Jabborov</t>
+          <t>Ismail Jabbarov</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -15466,12 +15482,12 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>['Джаббаров Ісмаїл', 'Ismaił Dżabbarow', 'Ismoil Jabborov', 'Джаббаров Исмаил', 'Исмаил Джаббаров']</t>
+          <t>['[Ismaił Dżabbarow]', 'Джаббаров Исмаил']</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -15511,7 +15527,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
@@ -15640,12 +15656,12 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>['Inoyatov Rustam Rasulovich', 'Rüstem İnayetov', 'Іноятов Рустам Расулович', 'Иноятов Рустам Расулович', 'Rustam Inoyatov', 'روستام اينوياتوڤ', 'رستم عنایتوف', 'ルスタム・イノヤトフ', 'Rüstəm İnayətov', 'Rüstem Resuloviç İnayetov', 'Рустам Расулович Иноятов', 'Rustam Rasulovich Inoyatov']</t>
+          <t>['Rustam Inoyatov', 'Rüstem Resuloviç İnayetov', 'Rustam Rasulovich Inoyatov', 'Inoyatov Rustam Rasulovich', 'Рустам Расулович Иноятов']</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -15685,7 +15701,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Military Personnel', 'Politician']</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
@@ -15818,12 +15834,12 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>['Матлюбов Баходыр Ахмедович', 'Матлюбов Баҳодир Аҳмедович', 'Баходыр Ахмедович Матлюбов', 'Bahodir Matlyubov', 'バホディル・マトリュボフ', 'Баходыр Матлюбов', 'Баҳодир Аҳмедович Матлюбов']</t>
+          <t>['Баходыр Ахмедович Матлюбов', 'Матлюбов Баходыр Ахмедович', 'Баҳодир Аҳмедович Матлюбов', 'Bahodir Matlyubov']</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -15863,7 +15879,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
@@ -15996,12 +16012,12 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As']</t>
+          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>['Akmalʹ Kholmatovich', 'Акмаль Саидов', 'Akmal Xolmatovich Saidov', 'A Kh Saidov', 'Акмаль Холматович Саидов', 'Саидов Акмаль Холматович', '阿克马勒·塞多夫', 'Саидов Акмаль', '阿克馬勒·塞多夫', 'Akmal Saidov', 'Akmal Holmatovitsj Saidov']</t>
+          <t>['Akmalʹ Kholmatovich', 'Акмаль Саидов', 'Саидов Акмаль Холматович', 'Акмаль Холматович Саидов', 'A Kh Saidov', 'Саидов Акмаль', 'Akmal Xolmatovich Saidov']</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -16170,12 +16186,12 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>['Oqil Umrzoqovich Salimov', 'Oqil Salimov', '阿基尔·乌穆尔扎科维奇·萨利莫夫', 'Salimov Oqil Umrzoqovich', 'Салімов Акіл Умурзакович', 'Акыл Сәлимов', 'Акил Умурзакович Салимов', 'Салимов Акил Умурзакович']</t>
+          <t>['Oqil Umrzoqovich Salimov', 'Салимов Акил Умурзакович', 'Oqil Salimov']</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -16340,12 +16356,12 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>['Бахтыёр Рахімаў', 'Baxtiyor Rahimov', 'Бахтыяр Рахімаў']</t>
+          <t>['Baxtiyor Rahimov', 'Бахтыяр Рахімаў']</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -16385,7 +16401,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
@@ -16514,12 +16530,12 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>['Shavkat Karimov', 'Karimov Shavkat Ibrohimovich']</t>
+          <t>['Karimov Shavkat Ibrohimovich']</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -16559,7 +16575,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
@@ -16692,12 +16708,12 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>['Arthur Taimazov', 'Артур Тајмазов', 'Tajmazty Barisy Fyrt Artur', 'Артур Таймазов', 'Artur Taymasow', 'Artur Taimazow', 'Artur Taymazow', 'Taymazov', 'آرتور تایمازوف', 'Таймазов Артур Борисович', 'Artur Tajmazov', 'Artur Taimàzov', 'Artur Taimasow', 'Artur Taymazov', 'آرتور تایمازف', 'ارتور تایمازف', 'ارتور تايمازوف', 'Artur Taimazov', 'アルトゥール・タイマゾフ', 'Артур Борисович Таймазов', 'Artur Tajmazow', 'Таймазты Артур', 'Artur Taimasov', 'ארתור טאימזוב', 'Arthur Taymazov', 'Artur Borisovich Taymazov', 'არტურ ტაიმაზოვი', 'ارتور تایمازوف', '阿爾圖爾·泰馬佐夫', 'Taimasow', '아르투르 타이마조프']</t>
+          <t>['Taimasow', 'Артур Таймазов', 'ارتور تایمازوف', 'Arthur Taimazov', 'Artur Tajmazov', 'Taymazov', 'Artur Taymasow', 'Arthur Taymazov', '阿爾圖爾·泰馬佐夫', 'Artur Taymazow', 'Артур Борисович Таймазов', 'آرتور تایمازف', 'ارتور تایمازف', 'Artur Taimasow', 'Artur Taimazow', 'Artur Taymazov', 'Artur Taimazov', 'Artur Taimasov', 'Artur Borisovich Taymazov', 'Tajmazty Barisy Fyrt Artur']</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -16762,7 +16778,7 @@
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>['UZ-GEN-TT-AGHDO-RCA-1']</t>
+          <t>['UZ-GEN-TT-3U988-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -16870,12 +16886,12 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>['Akmal Burxanov Eshondedayevich', 'Акмал Эшондедаевич Бурханов', 'Akmal Burxanov', 'Бурханов Акмал Эшондедаевич']</t>
+          <t>['Akmal Burxanov Eshondedayevich', 'Akmal Burxanov', 'Бурханов Акмал Эшондедаевич']</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -17052,12 +17068,12 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>['Каримова Гульнара', 'گلنارا کریموا', 'Gulnara Karimowa', 'Gülnare Kerimova', 'Гульнара Ісламаўна Карымава', 'Գուլնարա Քարիմովա', 'Гүлнара Каримова', 'جلنار كريموفا', 'جولنارا كاريموفا', 'Гүлнора Каримова', 'Goulnora Karimova', 'گلنارهٔ کریموا', '굴노라 카리모바', 'Карімова Гульнара Ісламівна', 'גולנרה קרימובה', 'Gülnare İslamovna Kerimova', 'グリナラ・カリモフ', 'ဂူလ်နာရာကရီမိုဗာ', 'Goulnara Karimova', 'گلناره کریموا', 'グリナラ・カリモヴァ', 'Гульнара Каримова', 'Gulnara Islomovna Karimova', 'Gulnora Islomovna Karimova', 'Gulnara Islamovna Karimovna', 'Гульнара Карымава', 'Gulnora Karimovová', 'Гульнара Исламовна Каримова', 'Gülnarə Kərimova', 'Googoosha', 'Karimova', 'Гүлнәр Каримова', 'গুলনারা করিমোভা', 'Гулнора Каримова', '古爾諾拉·卡麗莫娃', 'გულნარა ქარიმოვა', 'Qoshiq', 'Гугуша', 'Каримова Гульнара Исламовна', 'Gulnara Karimova', 'Каримова Гүлнара', 'گولنارا کریموا', 'Gulnara Islamovna Karimova', 'Gulnora Karimova', '굴나라 카리모바']</t>
+          <t>['굴나라 카리모바', 'Gulnara Islamovna Karimovna', 'Googoosha', 'Qoshiq', 'گلنارا کریموا', 'Gülnare İslamovna Kerimova', 'Gulnara Karimova', 'Каримова Гүлнара', 'Гугуша', 'Гүлнора Каримова', 'Гулнора Каримова', 'Каримова Гульнара Исламовна', 'グリナラ・カリモフ', 'Гульнара Каримова', 'جولنارا كاريموفا', 'Gulnora Karimova', 'Gulnara Islomovna Karimova', 'Gulnara Karimowa', 'Gulnora Islomovna Karimova', 'گولنارا کریموا', 'Goulnora Karimova', 'Karimova', 'Goulnara Karimova', 'گلنارهٔ کریموا', 'Каримова Гульнара', 'Gulnara Islamovna Karimova']</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -17097,7 +17113,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Entrepreneur', 'Music Arranger', 'Politician', 'Singer', 'Translator']</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
@@ -17122,7 +17138,7 @@
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>['UZ-GEN-TK-67MWV-RCA-1', 'UZ-GEN-LKT-E761N-RCA-1']</t>
+          <t>['UZ-GEN-TK-BEU9O-RCA-1', 'UZ-GEN-LKT-7C98Z-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -17230,12 +17246,12 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As']</t>
+          <t>['Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>['Кудбиев Шерзод Давлятович', 'Sherzod Davlyatovich Qudbiyev', 'Sherzod Kudbiev', 'Sherzod Qudbiyev']</t>
+          <t>['Sherzod Kudbiev', 'Sherzod Davlyatovich Qudbiyev']</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -17275,7 +17291,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Civil Servant', 'Politician']</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
@@ -17404,12 +17420,12 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>['Расул Қыдыралиұлы Көшербаев', 'Rasul Kusherbayev', 'Кушербаев Расул Хидралиевич', 'Rasul Kusherbaev', 'Расул Кӯшербоев', 'Кушербаєв Расул Кгідралійович']</t>
+          <t>['Rasul Kusherbaev']</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -17582,12 +17598,12 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>['肖開提·米爾則亞耶夫', 'Schawkat Miromonowitsch Mirsijojew', 'Шәүкәт Мираман улы Мирзияев', 'Šavkat Mirzijojev', 'Мирзиёев Шавкат Миромонович', 'Shovqat Mirziyoyev', 'Sjavkat Miromonovitj Mirzijajev', 'Mirziyoyev', 'シャフカット・ミルジヨエ', 'شوكت ميرضيايف', 'شوکت میرضیایف', '샵카트 미르지요예프', '米尔济约耶夫', 'Shavkat Miromonovich Mirziyoyev', 'Şevket Miramanoviç Mirziyoyev', 'சவ்காத் மிர்சியோயெவ்', 'شوکت میرضیایئف', 'Шавкат Мирзияев', 'Şavkat Mirziyoyev', 'Šavkats Mirzijojevs', 'شەوکەت میرزیایێڤ', 'Ŝavkat Mirzijojev', 'Мирзиёев Шавкат Мираманович', 'Шавкат Міромонович Мірзійоєв', 'Шавқат Миромонович Мирзиёев', 'Шаўкат Мірзіяеў', '沙夫卡特·米尔济约耶夫', 'Šavkat Mirzijajev', 'შავკათ მირზიიოევი', 'Chavkat Mirziyoyev', 'Shavkat Mirziyoyev', 'Şöwket Mirziýoýew', 'Sjavkat Mirzijojev', '샵카트 미로모노비치 미르지요예프', 'Szawkat Mirzijajew', 'Шавкат Мірзійоєв', 'ชัฟแกต มือร์ซียอยิฟ', 'ሻቭካት ሚርዚዮየቭ', 'Szawkat Miromonowicz Mirzijojew', 'Шавкат Мирзијоев', 'Ŝavkat Miromonoviĉ Mirzijojev', 'ഷൌക്കത്ത് മിർസിയോയേവ്', 'Շավկաթ Միրզիյոև', '肖開提·米爾濟約耶夫', 'Шаўкат Мірамонавіч Мірзіяеў', 'Şevket Mirziyoyev', 'Chavkat Mirzioïev', 'Sjavkat Miromonovitj Mirzijojev', 'Шәукет Міраманұлы Мірзияев', 'Šavkat Miromonovič Mirzijojev', 'Шәүкәт Мирзияев', 'Σαβκάτ Μιρζιγιάγιεφ', 'শাভকাত মির্জিয়োয়েভ', 'Шавкат Мирзиёев', 'Şövkət Mirzəyev', 'שבקט מירזייאיב', 'Мирзиёев', 'シャヴカト・ミルズィヤエフ', '米爾濟約耶夫', 'シャフカット・ミルジョーエフ', 'Sjavkat Mirzijajev', 'Шавкат Миромонович Мирзиёев', 'Шавкат Мирзијојев', 'Mirziyoyev Shavkat Miromonovich', 'শ্বাভকত মিৰ্জিয়েভ', 'Мирзиёев Шавкат', 'ساۋكات مىرزىيويەۋ', 'शौकत मिर्ज़िएव', 'Schawkat Mirsijojew', 'Shavkat Miromon Filius Mirziyoyev', 'Șavkat Miromonovici Mirziyoyev', 'Shavkat Mirziyayev', 'Mirziyayev Shavkat Miramanovich', 'Šavkatas Mirzijajevas']</t>
+          <t>['Shovqat Mirziyoyev', 'Mirziyoyev Shavkat Miromonovich', 'Szawkat Mirzijajew', 'Мирзиёев Шавкат Мираманович', 'Мирзиёев', 'Shavkat Miromon Filius Mirziyoyev', 'Şövkət Mirzəyev', 'Sjavkat Miromonovitj Mirzijojev', '米尔济约耶夫', 'Шавкат Миромонович Мирзиёев', 'シャフカット・ミルジヨエ', 'シャフカット・ミルジョーエフ', 'Мирзиёев Шавкат', 'Sjavkat Mirzijajev', 'Šavkat Mirzijojev', 'Šavkat Miromonovič Mirzijojev', 'Sjavkat Miromonovitj Mirzijajev', 'Shavkat Mirziyayev', 'Шавкат Мирзияев', '[Chavkat Mirzioïev]', 'Шавкат Мирзиёев', 'Mirziyoyev', 'Mirziyayev Shavkat Miramanovich', 'Şevket Miramanoviç Mirziyoyev', 'Szawkat Miromonowicz Mirzijojew', 'Sjavkat Mirzijojev', 'Schawkat Miromonowitsch Mirsijojew', 'Шавқат Миромонович Мирзиёев', 'Shavkat Mirziyoyev', 'Chavkat Mirziyoyev', 'Shavkat Miromonovich Mirziyoyev', 'Шавкат Міромонович Мірзійоєв', '샵카트 미로모노비치 미르지요예프', 'Ŝavkat Miromonoviĉ Mirzijojev', 'Шәукет Міраманұлы Мірзияев', 'Шаўкат Мірзіяеў', 'Шәүкәт Мираман улы Мирзияев']</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -17637,22 +17653,22 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>['2016-12-14', '2016-09-08', '2003-12-12']</t>
+          <t>['2016-09-08', '2016-12-14', '2003-12-12']</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>[None, '2016-12-14', '2016-12-14']</t>
+          <t>['2016-12-14', None, '2016-12-14']</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>['Partner', 'Child', 'Child']</t>
+          <t>['Child', 'Child', 'Partner']</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>['UZ-GEN-ZM-AJQOP-RCA-1', 'UZ-GEN-SM-H3YI1-RCA-1', 'UZ-GEN-SM-QZY37-RCA-1']</t>
+          <t>['UZ-GEN-SM-94271-RCA-1', 'UZ-GEN-SM-04LJS-RCA-1', 'UZ-GEN-ZM-WRJX2-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -17760,12 +17776,12 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>['エリョール・ガニエフ', 'اليور جانييف', 'Ganiyev', '叶瘳尔·加尼耶夫', 'Ганиев Элёр Маджидович', 'Elyor Gʻaniyev', 'Elyor Qəniyev', 'Elyor Ganiyev', '叶瘳尔·马吉多维奇·加尼耶夫']</t>
+          <t>['Elyor Ganiyev', '叶瘳尔·马吉多维奇·加尼耶夫', 'Ganiyev']</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -17805,7 +17821,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
@@ -17938,12 +17954,12 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>['Alisher Abdualiyev', 'Абдуалієв Алішер Хабібуллаєвич', 'Alisher Abdualiev', 'Абдуалиев Алишер Хабибуллаевич']</t>
+          <t>['Alisher Abdualiev']</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -17983,7 +17999,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
@@ -18116,12 +18132,12 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>['伊斯马季拉·埃尔加舍夫', '伊斯馬季拉·埃爾加舍夫', 'Ismatilla Ergashev', '伊斯马季拉·埃尔加捨夫', 'İsmətulla İrqaşev', 'عصمتيلا ارجاشيف']</t>
+          <t>['伊斯马季拉·埃尔加捨夫', 'Ismatilla Ergashev']</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -18161,7 +18177,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Diplomat', 'Politician']</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
@@ -18294,12 +18310,12 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>['Bakhodir Nizamovich Kurbanov', 'Баходир Курбанов', 'バホディル・クルバノフ', 'Bahodir Nizomovich Qurbonov', 'Bahadır Kurbanov', 'Bahadır Nizamoğlu Kurbanov', 'Bahodir Qurbonov', 'Баходир Низамович Курбанов', 'Bakhodir Kurbanov', 'باخودیر کوربانف']</t>
+          <t>['[Bahadır Kurbanov]', 'Bakhodir Nizamovich Kurbanov', 'Bahodir Nizomovich Qurbonov', 'Bahadır Nizamoğlu Kurbanov', 'Баходир Курбанов']</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -18472,12 +18488,12 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>['タンジナ・ナルバーエバ', 'Тәнзилә Нарбаева', '탄질라 나르바예바', 'Tənzilə Narbayeva', 'تنزیلا نورباوا', 'Tanzila Kamalovna Narbaeva', 'Тәнзила Камалқызы Норбаева', 'Tenzile Narbayeva', 'Tanzila Kamalovna Narbayeva', 'タンジラ・ナルバーエバ', 'Tenzile Kemalkızı Narbayeva', 'タンジラ・ノルバエヴァ', 'Tanzila Norbaeva', 'Танзила Норбоева', 'Tənzila Kamalovna Narbayeva', 'Тәнзилә Норбаева', 'Tanzila Norboeva', 'تنزیلہ نور بائیوا', 'Tanzila Norboyeva', 'Тәнзилә Камалқызы Нарбаева', 'Танзила Нарбаева', 'Танзила Камаловна Нарбаева', 'Танзила Камалқызы Нарбаева', 'ტანზილა ნარბაევა', 'Tanzila Narbaeva', 'Танзила Норбаева']</t>
+          <t>['Tanzila Kamalovna Narbayeva', 'Tanzila Norboeva', 'Tanzila Kamalovna Narbaeva', 'Тәнзилә Камалқызы Нарбаева', 'Tanzila Narbaeva', 'Тәнзилә Нарбаева', 'Tənzila Kamalovna Narbayeva', 'Танзила Норбаева', 'Тәнзилә Норбаева', 'Танзила Нарбаева', 'Tenzile Kemalkızı Narbayeva', 'タンジラ・ナルバーエバ', 'Тәнзила Камалқызы Норбаева', 'タンジラ・ノルバエヴァ']</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -18650,12 +18666,12 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>['Murad Nazarov', 'Murod Nazarov', 'ムロド・ナザロフ', 'Мурад Назаров', 'Назаров Мурад']</t>
+          <t>['Назаров Мурад', 'Murad Nazarov', 'Murod Nazarov']</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -18695,7 +18711,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
@@ -18865,7 +18881,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
@@ -18998,12 +19014,12 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>['穆罕默德·薩利赫', 'Muhammad Salih', 'Мухаммад Салих', 'Muhammad Solih', 'محمد ساليه', 'محمد صالح', 'Muhammad SolihМуҳаммад Солиҳ', 'Muhammed Salih', '穆罕默德·萨利赫']</t>
+          <t>['Muhammad SolihМуҳаммад Солиҳ', 'Muhammad Salih']</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -19043,7 +19059,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Dissident', 'Linguist', 'Poet', 'Politician', 'Translator']</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
@@ -19134,7 +19150,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/2b/UbaydullayevKhikmatilla.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/KhikmatUbay.jpg</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -19176,12 +19192,12 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>['Hikmat Ubaydullaev', 'Khikmat Pulatov', 'Убайдуллаев Хикмат', 'Хикмат Пулатов', 'Hikmetilla Ubaydullaev', 'Ҳикматилла Шухратиллаевич Убайдуллаев', 'Хикматилла Пулатов', 'Убайдуллаев Хикматилла Шухратиллаевич', 'Убайдуллаєв Хікматілла Шухратіллаєвич', 'Пулатов Хикматилла', 'Polatov Hikmatilla', 'Убайдуллаєв Хікматілла', 'Hikmat Polatov', 'Убайдуллаев Хикматилла', 'Хікматілла Убайдуллаєв', 'Ubaydullayev Khikmatilla', 'Убайдуллаев Хикматулла', 'Pulatov Khikmat', 'Убайдуллаєв Хікмат', 'Khikmatilla Pulatov', 'Ubaydullaev Hikmatilla', 'Ubaydullayev Khikmat', 'Пулатов Хикмат', 'Хикматулла Убайдуллаев', 'Ubaydullaev Hikmat', 'Хикмат Убайдуллаев', 'Pulatov Khikmatilla', 'Хикматилла Убайдуллаев']</t>
+          <t>['Пулатов Хикматилла', 'Ubaydullaev Hikmat', 'Убайдуллаєв Хікмат', 'Хикмат Пулатов', 'Хикмат Убайдуллаев', 'Hikmat Polatov', 'Пулатов Хикмат', 'Khikmat Pulatov', 'Khikmatilla Pulatov', 'Убайдуллаев Хикмат', 'Убайдуллаев Хикматилла', 'Ҳикматилла Шухратиллаевич Убайдуллаев', 'Убайдуллаєв Хікматілла', 'Polatov Hikmatilla', 'Hikmetilla Ubaydullaev', 'Ubaydullayev Khikmat', 'Pulatov Khikmatilla', 'Хикматулла Убайдуллаев', 'Хикматилла Убайдуллаев', 'Убайдуллаев Хикматулла', 'Хикматилла Пулатов', 'Hikmat Ubaydullaev', 'Pulatov Khikmat', 'Хікматілла Убайдуллаєв']</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -19221,7 +19237,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Blogger', 'Journalist', 'Politician']</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
@@ -19354,12 +19370,12 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>['Original Script Name', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Original Script Name', 'Also Known As']</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>['Борий Батырұлы Әлиханов', 'Boriy Alikhanov', 'Борий Батырович Алиханов', 'Boriy Alixanov', 'Алиханов Борий Батырович']</t>
+          <t>['Алиханов Борий Батырович', 'Boriy Alikhanov']</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -19528,12 +19544,12 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>['Umarov Otabek', 'Умаров Отабек Мухаммадалиевич', 'Otabek Umarov', 'Умаров Отабек Мухаммадалиеви']</t>
+          <t>['Otabek Umarov']</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -19573,7 +19589,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Businessperson', 'Sports Executive']</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
@@ -19598,7 +19614,7 @@
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>['UZ-GEN-SM-QZY37-RCA-1']</t>
+          <t>['UZ-GEN-SM-04LJS-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -19702,12 +19718,12 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>['Zamira Mutalova', 'Муталова Замира', 'Замира Муталова', 'ضمیره موتالووا', 'Моталова Замира']</t>
+          <t>['Zamira Mutalova', 'Муталова Замира']</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -19747,7 +19763,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
@@ -19917,7 +19933,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
@@ -20054,12 +20070,12 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Also Known As', 'Also Known As', 'Also Known As', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As', 'Also Known As', 'Original Script Name', 'Also Known As', 'Original Script Name']</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>['Mirziyoyeva Saida', 'Saida Mirziyoyeva', 'Саида Мирзиёева]', 'Saida Mirzijojevová', 'Саида Шавкатқызы Мирзиёева', 'Saide Mirziyoyeva', 'Saida Shavkatovna Mirziyoyeva', 'Saida Mirzijojeva', 'سعیده میرضیایف', 'Սաիդա Միրզիյոևա', '赛义达·米尔济约耶娃', 'Saida Šavkatovna Mirzijojevová', 'Saide Şevketovna Mirziyoyeva', '사이다 미르지요예바']</t>
+          <t>['Mirziyoyeva Saida', 'Saida Mirziyoyeva', 'Saida Mirzijojevová', 'Saida Shavkatovna Mirziyoyeva', 'Saide Şevketovna Mirziyoyeva']</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -20099,7 +20115,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Politician']</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
@@ -20119,12 +20135,12 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>['Mother', 'Sibling', 'Partner']</t>
+          <t>['Partner', 'Mother', 'Sibling']</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>['UZ-GEN-ZM-AJQOP-RCA-1', 'UZ-GEN-SM-QZY37-RCA-1', 'UZ-GEN-OT-Y6OMQ-RCA-1']</t>
+          <t>['UZ-GEN-OT-WQLUE-RCA-1', 'UZ-GEN-ZM-WRJX2-RCA-1', 'UZ-GEN-SM-04LJS-RCA-1']</t>
         </is>
       </c>
     </row>
@@ -20224,12 +20240,12 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>['Also Known As', 'Original Script Name', 'Original Script Name']</t>
+          <t>['Also Known As']</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>['Nodirjon Abduvaliev', 'Абдувалієв Нодіржон Рахматжонович', 'Абдувалиев Нодиржон Рахматжонович']</t>
+          <t>['Nodirjon Abduvaliev']</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -20301,12 +20317,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UZ-GEN-LK-SO4AK-RCA-1</t>
+          <t>UZ-GEN-NU-7FW1K-RCA-1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lyubov Kabaeva</t>
+          <t>Nilufar Usmonova</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -20463,12 +20479,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UZ-GEN-TK-67MWV-RCA-1</t>
+          <t>UZ-GEN-IP-4LXIG-RCA-1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tatyana Karimova</t>
+          <t>Ivan Putin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -20625,12 +20641,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UZ-GEN-ZM-AJQOP-RCA-1</t>
+          <t>UZ-GEN-VPJ-C1JFM-RCA-1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ziroat Mirziyoyeva</t>
+          <t>Vladimir Putin Jr</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -20787,12 +20803,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UZ-GEN-TT-AGHDO-RCA-1</t>
+          <t>UZ-GEN-GK-75XA0-RCA-1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timur Taymazov</t>
+          <t>Gulnara Karimova</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -20949,7 +20965,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UZ-GEN-LKT-E761N-RCA-1</t>
+          <t>UZ-GEN-LKT-7C98Z-RCA-1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -21111,12 +21127,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UZ-GEN-SM-QZY37-RCA-1</t>
+          <t>UZ-GEN-SM-94271-RCA-1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shakhnoza Mirziyoyeva</t>
+          <t>Saida Mirziyoyeva</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -21273,12 +21289,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UZ-GEN-IH-6G5P2-RCA-1</t>
+          <t>UZ-GEN-SM-04LJS-RCA-1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ibrohim Hakimov</t>
+          <t>Shakhnoza Mirziyoyeva</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -21435,12 +21451,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UZ-GEN-IK-2A3V8-RCA-1</t>
+          <t>UZ-GEN-IH-0IVDH-RCA-1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Islam Karimov</t>
+          <t>Ibrohim Hakimov</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -21597,12 +21613,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UZ-GEN-OT-Y6OMQ-RCA-1</t>
+          <t>UZ-GEN-IK-5A8DA-RCA-1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Oybek Tursunov</t>
+          <t>Islam Karimov</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -21759,12 +21775,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UZ-GEN-NU-DE5TE-RCA-1</t>
+          <t>UZ-GEN-ZM-WRJX2-RCA-1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nilufar Usmonova</t>
+          <t>Ziroat Mirziyoyeva</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -21921,12 +21937,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UZ-GEN-IP-W3VCD-RCA-1</t>
+          <t>UZ-GEN-OT-WQLUE-RCA-1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ivan Putin</t>
+          <t>Oybek Tursunov</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -22083,12 +22099,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UZ-GEN-VPJ-KXHV0-RCA-1</t>
+          <t>UZ-GEN-LK-1HSLO-RCA-1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vladimir Putin Jr</t>
+          <t>Lyubov Kabaeva</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -22245,12 +22261,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UZ-GEN-GK-UYW9Q-RCA-1</t>
+          <t>UZ-GEN-TK-BEU9O-RCA-1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gulnara Karimova</t>
+          <t>Tatyana Karimova</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -22407,12 +22423,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UZ-GEN-SM-H3YI1-RCA-1</t>
+          <t>UZ-GEN-TT-3U988-RCA-1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Saida Mirziyoyeva</t>
+          <t>Timur Taymazov</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
